--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_BASKONIA VITORIA-GASTEIZ.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_BASKONIA VITORIA-GASTEIZ.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>13.4412</v>
+        <v>24.5694</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1738</v>
+        <v>41.0089</v>
       </c>
       <c r="F2" t="n">
-        <v>3.266999999999999</v>
+        <v>-16.4392</v>
       </c>
       <c r="G2" t="n">
-        <v>4.790999999999999</v>
+        <v>1.7716</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5883</v>
+        <v>-0.4104000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.798</v>
+        <v>2.181700000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>23.8563</v>
+        <v>39.0934</v>
       </c>
       <c r="K2" t="n">
-        <v>14.2824</v>
+        <v>16.4575</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5741</v>
+        <v>22.636</v>
       </c>
       <c r="M2" t="n">
-        <v>-19.066</v>
+        <v>-37.3222</v>
       </c>
       <c r="N2" t="n">
-        <v>-5.6941</v>
+        <v>-16.8677</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.3716</v>
+        <v>-20.4543</v>
       </c>
       <c r="P2" t="n">
-        <v>18.5562</v>
+        <v>-0.9277000000000004</v>
       </c>
       <c r="Q2" t="n">
-        <v>-14.3815</v>
+        <v>-45.6947</v>
       </c>
       <c r="R2" t="n">
-        <v>32.9377</v>
+        <v>44.7672</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2989</v>
+        <v>-4.7185</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.518</v>
+        <v>-1.9774</v>
       </c>
       <c r="U2" t="n">
-        <v>6.817</v>
+        <v>-2.7408</v>
       </c>
       <c r="V2" t="n">
-        <v>-14.2048</v>
+        <v>28.4443</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2166</v>
+        <v>49.5872</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.4214</v>
+        <v>-21.143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>12.8523</v>
+        <v>12.2368</v>
       </c>
       <c r="E3" t="n">
-        <v>33.1416</v>
+        <v>30.5643</v>
       </c>
       <c r="F3" t="n">
-        <v>-20.289</v>
+        <v>-18.3283</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7716</v>
+        <v>-3.136700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4104000000000001</v>
+        <v>-2.7042</v>
       </c>
       <c r="I3" t="n">
-        <v>2.181700000000001</v>
+        <v>-0.4319999999999988</v>
       </c>
       <c r="J3" t="n">
-        <v>39.0934</v>
+        <v>46.4735</v>
       </c>
       <c r="K3" t="n">
-        <v>16.4575</v>
+        <v>18.9816</v>
       </c>
       <c r="L3" t="n">
-        <v>22.636</v>
+        <v>27.4921</v>
       </c>
       <c r="M3" t="n">
-        <v>-37.3222</v>
+        <v>-49.6101</v>
       </c>
       <c r="N3" t="n">
-        <v>-16.8677</v>
+        <v>-21.6861</v>
       </c>
       <c r="O3" t="n">
-        <v>-20.4543</v>
+        <v>-27.9244</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9277000000000004</v>
+        <v>-12.5254</v>
       </c>
       <c r="Q3" t="n">
-        <v>-45.6947</v>
+        <v>-76.3125</v>
       </c>
       <c r="R3" t="n">
-        <v>44.7672</v>
+        <v>63.7872</v>
       </c>
       <c r="S3" t="n">
-        <v>-16.4356</v>
+        <v>-6.1591</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.844799999999999</v>
+        <v>-8.878399999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.5907</v>
+        <v>2.7191</v>
       </c>
       <c r="V3" t="n">
-        <v>28.4443</v>
+        <v>34.0578</v>
       </c>
       <c r="W3" t="n">
-        <v>49.5872</v>
+        <v>69.2812</v>
       </c>
       <c r="X3" t="n">
-        <v>-21.143</v>
+        <v>-35.2234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>6.337</v>
+        <v>10.4565</v>
       </c>
       <c r="E4" t="n">
-        <v>23.6354</v>
+        <v>9.0214</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.2983</v>
+        <v>1.4349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0403</v>
+        <v>4.790999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>8.2492</v>
+        <v>8.5883</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.2089</v>
+        <v>-3.798</v>
       </c>
       <c r="J4" t="n">
-        <v>26.4097</v>
+        <v>23.8563</v>
       </c>
       <c r="K4" t="n">
-        <v>15.1472</v>
+        <v>14.2824</v>
       </c>
       <c r="L4" t="n">
-        <v>11.2621</v>
+        <v>9.5741</v>
       </c>
       <c r="M4" t="n">
-        <v>-25.3694</v>
+        <v>-19.066</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.898400000000001</v>
+        <v>-5.6941</v>
       </c>
       <c r="O4" t="n">
-        <v>-18.4713</v>
+        <v>-13.3716</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6236</v>
+        <v>18.5562</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.2415</v>
+        <v>-14.3815</v>
       </c>
       <c r="R4" t="n">
-        <v>30.6179</v>
+        <v>32.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>29.3988</v>
+        <v>1.3143</v>
       </c>
       <c r="T4" t="n">
-        <v>25.3376</v>
+        <v>-3.6705</v>
       </c>
       <c r="U4" t="n">
-        <v>4.0609</v>
+        <v>4.9849</v>
       </c>
       <c r="V4" t="n">
-        <v>-22.4782</v>
+        <v>-14.2048</v>
       </c>
       <c r="W4" t="n">
-        <v>4.1296</v>
+        <v>3.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-26.6077</v>
+        <v>-17.4214</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>4.359299999999999</v>
+        <v>8.4862</v>
       </c>
       <c r="E5" t="n">
-        <v>9.6602</v>
+        <v>10.8476</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.3011</v>
+        <v>-2.3612</v>
       </c>
       <c r="G5" t="n">
         <v>-7.643699999999999</v>
@@ -844,13 +844,13 @@
         <v>32.7054</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6377</v>
+        <v>2.4893</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2755</v>
+        <v>2.4626</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.9135</v>
+        <v>0.02649999999999986</v>
       </c>
       <c r="V5" t="n">
         <v>-7.9308</v>
@@ -877,13 +877,13 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2744</v>
+        <v>2.044400000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.4946</v>
+        <v>-3.8223</v>
       </c>
       <c r="F6" t="n">
-        <v>7.7689</v>
+        <v>5.866900000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-3.064200000000001</v>
@@ -922,13 +922,13 @@
         <v>22.0356</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4884</v>
+        <v>-1.7185</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.2881</v>
+        <v>-1.6159</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7996</v>
+        <v>-0.1026999999999998</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3632000000000001</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0177</v>
+        <v>0.9916</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0669</v>
+        <v>0.0078</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0846</v>
+        <v>0.9838</v>
       </c>
       <c r="G7" t="n">
         <v>0.629</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0751</v>
+        <v>-0.1013</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>-0.1494</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4451000000000001</v>
+        <v>-0.6202999999999994</v>
       </c>
       <c r="E8" t="n">
-        <v>20.484</v>
+        <v>3.893500000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-20.039</v>
+        <v>-4.5135</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.136700000000001</v>
+        <v>0.9312999999999996</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7042</v>
+        <v>0.6893999999999991</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4319999999999988</v>
+        <v>0.2417000000000005</v>
       </c>
       <c r="J8" t="n">
-        <v>46.4735</v>
+        <v>29.2144</v>
       </c>
       <c r="K8" t="n">
-        <v>18.9816</v>
+        <v>10.3654</v>
       </c>
       <c r="L8" t="n">
-        <v>27.4921</v>
+        <v>18.8494</v>
       </c>
       <c r="M8" t="n">
-        <v>-49.6101</v>
+        <v>-28.2837</v>
       </c>
       <c r="N8" t="n">
-        <v>-21.6861</v>
+        <v>-9.6762</v>
       </c>
       <c r="O8" t="n">
-        <v>-27.9244</v>
+        <v>-18.6075</v>
       </c>
       <c r="P8" t="n">
-        <v>-12.5254</v>
+        <v>1.391899999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-76.3125</v>
+        <v>-37.5766</v>
       </c>
       <c r="R8" t="n">
-        <v>63.7872</v>
+        <v>38.9685</v>
       </c>
       <c r="S8" t="n">
-        <v>-17.9508</v>
+        <v>-5.654199999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-18.9589</v>
+        <v>-6.6022</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0079</v>
+        <v>0.9477</v>
       </c>
       <c r="V8" t="n">
-        <v>34.0578</v>
+        <v>2.7115</v>
       </c>
       <c r="W8" t="n">
-        <v>69.2812</v>
+        <v>18.8567</v>
       </c>
       <c r="X8" t="n">
-        <v>-35.2234</v>
+        <v>-16.1452</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3301</v>
+        <v>-2.2065</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06399999999999996</v>
+        <v>-1.0076</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.266</v>
+        <v>-1.1988</v>
       </c>
       <c r="G9" t="n">
         <v>-2.659</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0764</v>
+        <v>-0.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9005000000000001</v>
+        <v>-0.04310000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8242</v>
+        <v>-0.757</v>
       </c>
       <c r="V9" t="n">
         <v>0.7886</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SAMANIC</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7371</v>
+        <v>-2.527500000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9848</v>
+        <v>0.4743000000000004</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7523</v>
+        <v>-3.002</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5566</v>
+        <v>-2.4158</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7791</v>
+        <v>1.8331</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3358</v>
+        <v>-4.2489</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1095</v>
+        <v>4.8162</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8527</v>
+        <v>5.5092</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7430999999999999</v>
+        <v>-0.6929000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6662</v>
+        <v>-7.232</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0736</v>
+        <v>-3.6764</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5928</v>
+        <v>-3.556</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7835</v>
+        <v>7.886699999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.958699999999999</v>
+        <v>-4.6394</v>
       </c>
       <c r="R10" t="n">
-        <v>4.1752</v>
+        <v>12.5258</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0774</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.6387</v>
+        <v>-1.3113</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4388</v>
+        <v>0.3133</v>
       </c>
       <c r="V10" t="n">
-        <v>2.6805</v>
+        <v>-7.0004</v>
       </c>
       <c r="W10" t="n">
-        <v>5.502800000000001</v>
+        <v>1.6083</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8223</v>
+        <v>-8.608700000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5196</v>
+        <v>-3.4081</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6681</v>
+        <v>18.7689</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8514</v>
+        <v>-22.1773</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4158</v>
+        <v>6.499599999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8331</v>
+        <v>23.421</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.2489</v>
+        <v>-16.9214</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8162</v>
+        <v>47.6823</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5092</v>
+        <v>38.9335</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6929000000000001</v>
+        <v>8.748800000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.232</v>
+        <v>-41.183</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.6764</v>
+        <v>-15.5125</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.556</v>
+        <v>-25.6701</v>
       </c>
       <c r="P11" t="n">
-        <v>7.886699999999999</v>
+        <v>-3.2474</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.6394</v>
+        <v>-54.5091</v>
       </c>
       <c r="R11" t="n">
-        <v>12.5258</v>
+        <v>51.2618</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.9898</v>
+        <v>-12.454</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.454</v>
+        <v>-9.1717</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5364</v>
+        <v>-3.2822</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.0004</v>
+        <v>5.7934</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6083</v>
+        <v>34.7669</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.608700000000001</v>
+        <v>-28.9735</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>L. SAMANIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.478299999999999</v>
+        <v>-3.6326</v>
       </c>
       <c r="E12" t="n">
-        <v>2.952700000000001</v>
+        <v>-1.5562</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.4311</v>
+        <v>-2.0763</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.9391</v>
+        <v>-1.5566</v>
       </c>
       <c r="H12" t="n">
-        <v>16.6147</v>
+        <v>1.7791</v>
       </c>
       <c r="I12" t="n">
-        <v>-21.5543</v>
+        <v>-3.3358</v>
       </c>
       <c r="J12" t="n">
-        <v>34.6962</v>
+        <v>1.1095</v>
       </c>
       <c r="K12" t="n">
-        <v>30.4128</v>
+        <v>1.8527</v>
       </c>
       <c r="L12" t="n">
-        <v>4.283200000000001</v>
+        <v>-0.7430999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-39.6351</v>
+        <v>-2.6662</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.7979</v>
+        <v>-0.0736</v>
       </c>
       <c r="O12" t="n">
-        <v>-25.8372</v>
+        <v>-2.5928</v>
       </c>
       <c r="P12" t="n">
-        <v>-13.4535</v>
+        <v>-2.7835</v>
       </c>
       <c r="Q12" t="n">
-        <v>-67.4982</v>
+        <v>-6.958699999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>54.0452</v>
+        <v>4.1752</v>
       </c>
       <c r="S12" t="n">
-        <v>19.051</v>
+        <v>-1.9729</v>
       </c>
       <c r="T12" t="n">
-        <v>13.4282</v>
+        <v>-1.2101</v>
       </c>
       <c r="U12" t="n">
-        <v>5.6227</v>
+        <v>-0.7628</v>
       </c>
       <c r="V12" t="n">
-        <v>-10.1374</v>
+        <v>2.6805</v>
       </c>
       <c r="W12" t="n">
-        <v>22.3259</v>
+        <v>5.502800000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-32.4633</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.1806</v>
+        <v>-9.5379</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.154799999999998</v>
+        <v>1.172999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.025700000000001</v>
+        <v>-10.7107</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9312999999999996</v>
+        <v>6.152</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6893999999999991</v>
+        <v>10.5133</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2417000000000005</v>
+        <v>-4.361499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>29.2144</v>
+        <v>28.5138</v>
       </c>
       <c r="K13" t="n">
-        <v>10.3654</v>
+        <v>18.0813</v>
       </c>
       <c r="L13" t="n">
-        <v>18.8494</v>
+        <v>10.4326</v>
       </c>
       <c r="M13" t="n">
-        <v>-28.2837</v>
+        <v>-22.3616</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.6762</v>
+        <v>-7.5678</v>
       </c>
       <c r="O13" t="n">
-        <v>-18.6075</v>
+        <v>-14.7937</v>
       </c>
       <c r="P13" t="n">
-        <v>1.391899999999999</v>
+        <v>-2.7835</v>
       </c>
       <c r="Q13" t="n">
-        <v>-37.5766</v>
+        <v>-33.8654</v>
       </c>
       <c r="R13" t="n">
-        <v>38.9685</v>
+        <v>31.0819</v>
       </c>
       <c r="S13" t="n">
-        <v>-17.2147</v>
+        <v>-4.2981</v>
       </c>
       <c r="T13" t="n">
-        <v>-14.65</v>
+        <v>-4.5123</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5649</v>
+        <v>0.2146999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>2.7115</v>
+        <v>-8.608700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>18.8567</v>
+        <v>11.0367</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.1452</v>
+        <v>-19.6454</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.5108</v>
+        <v>-12.2441</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.5374</v>
+        <v>6.7093</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9734</v>
+        <v>-18.9532</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.3224</v>
+        <v>1.0403</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.2194</v>
+        <v>8.2492</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.1029</v>
+        <v>-7.2089</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.6609</v>
+        <v>26.4097</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6162</v>
+        <v>15.1472</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.0447</v>
+        <v>11.2621</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.6614</v>
+        <v>-25.3694</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6031</v>
+        <v>-6.898400000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.0583</v>
+        <v>-18.4713</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0876</v>
+        <v>-1.6236</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.4226</v>
+        <v>-32.2415</v>
       </c>
       <c r="R14" t="n">
-        <v>5.334899999999999</v>
+        <v>30.6179</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8843000000000001</v>
+        <v>10.8176</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4543</v>
+        <v>8.411199999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5698</v>
+        <v>2.4063</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.2166</v>
+        <v>-22.4782</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.1296</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2166</v>
+        <v>-26.6077</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.7383</v>
+        <v>-13.3656</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.6604</v>
+        <v>-10.6501</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0776</v>
+        <v>-2.7153</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.992100000000001</v>
+        <v>-9.3224</v>
       </c>
       <c r="H15" t="n">
-        <v>9.138400000000001</v>
+        <v>-3.2194</v>
       </c>
       <c r="I15" t="n">
-        <v>-16.1301</v>
+        <v>-6.1029</v>
       </c>
       <c r="J15" t="n">
-        <v>1.785999999999999</v>
+        <v>-3.6609</v>
       </c>
       <c r="K15" t="n">
-        <v>6.3474</v>
+        <v>-1.6162</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.5616</v>
+        <v>-2.0447</v>
       </c>
       <c r="M15" t="n">
-        <v>-8.778</v>
+        <v>-5.6614</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7907</v>
+        <v>-1.6031</v>
       </c>
       <c r="O15" t="n">
-        <v>-11.5689</v>
+        <v>-4.0583</v>
       </c>
       <c r="P15" t="n">
-        <v>-14.149</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-33.6331</v>
+        <v>-7.4226</v>
       </c>
       <c r="R15" t="n">
-        <v>19.4841</v>
+        <v>5.334899999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7016</v>
+        <v>1.2609</v>
       </c>
       <c r="T15" t="n">
-        <v>2.162199999999999</v>
+        <v>0.4331</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5394999999999998</v>
+        <v>0.8278</v>
       </c>
       <c r="V15" t="n">
-        <v>2.701</v>
+        <v>-3.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>15.0244</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.3233</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>-19.6169</v>
+        <v>-17.5699</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.881500000000001</v>
+        <v>-15.8442</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.7357</v>
+        <v>-1.7257</v>
       </c>
       <c r="G16" t="n">
-        <v>6.152</v>
+        <v>-6.992100000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5133</v>
+        <v>9.138400000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.361499999999999</v>
+        <v>-16.1301</v>
       </c>
       <c r="J16" t="n">
-        <v>28.5138</v>
+        <v>1.785999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>18.0813</v>
+        <v>6.3474</v>
       </c>
       <c r="L16" t="n">
-        <v>10.4326</v>
+        <v>-4.5616</v>
       </c>
       <c r="M16" t="n">
-        <v>-22.3616</v>
+        <v>-8.778</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.5678</v>
+        <v>2.7907</v>
       </c>
       <c r="O16" t="n">
-        <v>-14.7937</v>
+        <v>-11.5689</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.7835</v>
+        <v>-14.149</v>
       </c>
       <c r="Q16" t="n">
-        <v>-33.8654</v>
+        <v>-33.6331</v>
       </c>
       <c r="R16" t="n">
-        <v>31.0819</v>
+        <v>19.4841</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.377</v>
+        <v>0.8698999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.567</v>
+        <v>0.9785</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.8098</v>
+        <v>-0.1084000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-8.608700000000001</v>
+        <v>2.701</v>
       </c>
       <c r="W16" t="n">
-        <v>11.0367</v>
+        <v>15.0244</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.6454</v>
+        <v>-12.3233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.1019</v>
+        <v>-23.0286</v>
       </c>
       <c r="E17" t="n">
-        <v>-11.6777</v>
+        <v>-9.094799999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.424100000000001</v>
+        <v>-13.9339</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.7822</v>
+        <v>-4.9391</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.554500000000001</v>
+        <v>16.6147</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2276000000000005</v>
+        <v>-21.5543</v>
       </c>
       <c r="J17" t="n">
-        <v>20.1659</v>
+        <v>34.6962</v>
       </c>
       <c r="K17" t="n">
-        <v>5.9549</v>
+        <v>30.4128</v>
       </c>
       <c r="L17" t="n">
-        <v>14.2113</v>
+        <v>4.283200000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-25.9481</v>
+        <v>-39.6351</v>
       </c>
       <c r="N17" t="n">
-        <v>-11.5094</v>
+        <v>-13.7979</v>
       </c>
       <c r="O17" t="n">
-        <v>-14.4387</v>
+        <v>-25.8372</v>
       </c>
       <c r="P17" t="n">
-        <v>-12.2934</v>
+        <v>-13.4535</v>
       </c>
       <c r="Q17" t="n">
-        <v>-49.6378</v>
+        <v>-67.4982</v>
       </c>
       <c r="R17" t="n">
-        <v>37.3444</v>
+        <v>54.0452</v>
       </c>
       <c r="S17" t="n">
-        <v>11.7731</v>
+        <v>5.501</v>
       </c>
       <c r="T17" t="n">
-        <v>9.6591</v>
+        <v>1.381</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1139</v>
+        <v>4.1198</v>
       </c>
       <c r="V17" t="n">
-        <v>-14.7998</v>
+        <v>-10.1374</v>
       </c>
       <c r="W17" t="n">
-        <v>8.1347</v>
+        <v>22.3259</v>
       </c>
       <c r="X17" t="n">
-        <v>-22.9346</v>
+        <v>-32.4633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-25.5232</v>
+        <v>-25.3545</v>
       </c>
       <c r="E18" t="n">
-        <v>5.040099999999999</v>
+        <v>-18.0633</v>
       </c>
       <c r="F18" t="n">
-        <v>-30.5629</v>
+        <v>-7.291299999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>6.499599999999999</v>
+        <v>-5.7822</v>
       </c>
       <c r="H18" t="n">
-        <v>23.421</v>
+        <v>-5.554500000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-16.9214</v>
+        <v>-0.2276000000000005</v>
       </c>
       <c r="J18" t="n">
-        <v>47.6823</v>
+        <v>20.1659</v>
       </c>
       <c r="K18" t="n">
-        <v>38.9335</v>
+        <v>5.9549</v>
       </c>
       <c r="L18" t="n">
-        <v>8.748800000000001</v>
+        <v>14.2113</v>
       </c>
       <c r="M18" t="n">
-        <v>-41.183</v>
+        <v>-25.9481</v>
       </c>
       <c r="N18" t="n">
-        <v>-15.5125</v>
+        <v>-11.5094</v>
       </c>
       <c r="O18" t="n">
-        <v>-25.6701</v>
+        <v>-14.4387</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.2474</v>
+        <v>-12.2934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-54.5091</v>
+        <v>-49.6378</v>
       </c>
       <c r="R18" t="n">
-        <v>51.2618</v>
+        <v>37.3444</v>
       </c>
       <c r="S18" t="n">
-        <v>-34.5687</v>
+        <v>7.521</v>
       </c>
       <c r="T18" t="n">
-        <v>-22.901</v>
+        <v>3.2735</v>
       </c>
       <c r="U18" t="n">
-        <v>-11.6677</v>
+        <v>4.2474</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7934</v>
+        <v>-14.7998</v>
       </c>
       <c r="W18" t="n">
-        <v>34.7669</v>
+        <v>8.1347</v>
       </c>
       <c r="X18" t="n">
-        <v>-28.9735</v>
+        <v>-22.9346</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>-35.2586</v>
+        <v>-32.3296</v>
       </c>
       <c r="E19" t="n">
-        <v>-13.5386</v>
+        <v>-11.244</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.7202</v>
+        <v>-21.086</v>
       </c>
       <c r="G19" t="n">
-        <v>-38.4462</v>
+        <v>-8.469799999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.3863</v>
+        <v>4.7202</v>
       </c>
       <c r="I19" t="n">
-        <v>-29.06</v>
+        <v>-13.19</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5290999999999999</v>
+        <v>15.4241</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8973</v>
+        <v>10.7653</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.4264</v>
+        <v>4.658600000000002</v>
       </c>
       <c r="M19" t="n">
-        <v>-37.9171</v>
+        <v>-23.8941</v>
       </c>
       <c r="N19" t="n">
-        <v>-14.2836</v>
+        <v>-6.0453</v>
       </c>
       <c r="O19" t="n">
-        <v>-23.6336</v>
+        <v>-17.8484</v>
       </c>
       <c r="P19" t="n">
-        <v>-17.8601</v>
+        <v>-1.6236</v>
       </c>
       <c r="Q19" t="n">
-        <v>-53.813</v>
+        <v>-33.4012</v>
       </c>
       <c r="R19" t="n">
-        <v>35.9527</v>
+        <v>31.7776</v>
       </c>
       <c r="S19" t="n">
-        <v>8.371500000000001</v>
+        <v>-6.7274</v>
       </c>
       <c r="T19" t="n">
-        <v>8.876199999999999</v>
+        <v>-2.5536</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5048000000000001</v>
+        <v>-4.1738</v>
       </c>
       <c r="V19" t="n">
-        <v>12.676</v>
+        <v>-15.5088</v>
       </c>
       <c r="W19" t="n">
-        <v>31.9271</v>
+        <v>9.2866</v>
       </c>
       <c r="X19" t="n">
-        <v>-19.2511</v>
+        <v>-24.7954</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>-47.6967</v>
+        <v>-43.2136</v>
       </c>
       <c r="E20" t="n">
-        <v>-20.8136</v>
+        <v>-22.4518</v>
       </c>
       <c r="F20" t="n">
-        <v>-26.8835</v>
+        <v>-20.762</v>
       </c>
       <c r="G20" t="n">
-        <v>-8.469799999999999</v>
+        <v>-38.4462</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7202</v>
+        <v>-9.3863</v>
       </c>
       <c r="I20" t="n">
-        <v>-13.19</v>
+        <v>-29.06</v>
       </c>
       <c r="J20" t="n">
-        <v>15.4241</v>
+        <v>-0.5290999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>10.7653</v>
+        <v>4.8973</v>
       </c>
       <c r="L20" t="n">
-        <v>4.658600000000002</v>
+        <v>-5.4264</v>
       </c>
       <c r="M20" t="n">
-        <v>-23.8941</v>
+        <v>-37.9171</v>
       </c>
       <c r="N20" t="n">
-        <v>-6.0453</v>
+        <v>-14.2836</v>
       </c>
       <c r="O20" t="n">
-        <v>-17.8484</v>
+        <v>-23.6336</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6236</v>
+        <v>-17.8601</v>
       </c>
       <c r="Q20" t="n">
-        <v>-33.4012</v>
+        <v>-53.813</v>
       </c>
       <c r="R20" t="n">
-        <v>31.7776</v>
+        <v>35.9527</v>
       </c>
       <c r="S20" t="n">
-        <v>-22.0946</v>
+        <v>0.4166999999999998</v>
       </c>
       <c r="T20" t="n">
-        <v>-12.123</v>
+        <v>-0.03700000000000003</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.971300000000001</v>
+        <v>0.4538000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-15.5088</v>
+        <v>12.676</v>
       </c>
       <c r="W20" t="n">
-        <v>9.2866</v>
+        <v>31.9271</v>
       </c>
       <c r="X20" t="n">
-        <v>-24.7954</v>
+        <v>-19.2511</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>37</v>
       </c>
       <c r="D21" t="n">
-        <v>-171.9651</v>
+        <v>-130.2539</v>
       </c>
       <c r="E21" t="n">
-        <v>14.54539999999999</v>
+        <v>28.7347</v>
       </c>
       <c r="F21" t="n">
-        <v>-186.5108</v>
+        <v>-158.9891</v>
       </c>
       <c r="G21" t="n">
         <v>-72.613</v>
@@ -2092,16 +2092,16 @@
         <v>549.7309</v>
       </c>
       <c r="S21" t="n">
-        <v>-57.12280000000001</v>
+        <v>-15.41079999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-38.98250000000001</v>
+        <v>-24.793</v>
       </c>
       <c r="U21" t="n">
-        <v>-18.1419</v>
+        <v>9.381699999999997</v>
       </c>
       <c r="V21" t="n">
-        <v>-14.3956</v>
+        <v>-14.39560000000001</v>
       </c>
       <c r="W21" t="n">
         <v>291.7162</v>
